--- a/docs/design-vi/ACSMS-SCR-030/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_ログ参照画面_v1.0.xlsx
+++ b/docs/design-vi/ACSMS-SCR-030/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_ログ参照画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1361,20 +1361,80 @@
       <c r="AG2" s="10" t="n"/>
       <c r="AH2" s="11" t="n"/>
     </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>Sửa lỗi thiếu đồng bộ với screen-design.md: chức năng xuất CSV chỉ xuất "trang đang hiển thị" (không xuất toàn bộ) nên không tồn tại kiểm tra giới hạn 5,000 dòng. Đánh dấu ACSMS-TC-030-034 là đã bãi bỏ (giữ nguyên ID, không đánh số lại). Xóa cụm "trong phạm vi 5,000 dòng" khỏi tiền đề/kết quả mong đợi của ACSMS-TC-030-033</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="19" t="inlineStr"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="19" t="inlineStr"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="AC2:AH2"/>
     <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="W1:AB1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="W3:AB3"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1539,7 +1599,7 @@
       <c r="Y2" s="23" t="n"/>
       <c r="Z2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AA2" s="22" t="n"/>
@@ -1555,7 +1615,7 @@
       <c r="AG2" s="23" t="n"/>
       <c r="AH2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="22" t="n"/>
@@ -2078,7 +2138,7 @@
       <c r="F4" s="11" t="n"/>
       <c r="G4" s="20" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="H4" s="10" t="n"/>
@@ -2851,7 +2911,7 @@
       <c r="Y2" s="23" t="n"/>
       <c r="Z2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AA2" s="22" t="n"/>
@@ -2867,7 +2927,7 @@
       <c r="AG2" s="23" t="n"/>
       <c r="AH2" s="21" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="22" t="n"/>
@@ -6484,7 +6544,7 @@
       <c r="E2" s="11" t="n"/>
       <c r="F2" s="20" t="inlineStr">
         <is>
-          <t>Kieu Thi Diem</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="G2" s="10" t="n"/>
@@ -14849,7 +14909,7 @@
       <c r="D50" s="11" t="n"/>
       <c r="E50" s="46" t="inlineStr">
         <is>
-          <t>Xuất CSV case bình thường (trong 5,000 dòng + UTF-8 BOM)</t>
+          <t>Xuất CSV case bình thường (chỉ trang đang hiển thị + UTF-8 BOM)</t>
         </is>
       </c>
       <c r="F50" s="10" t="n"/>
@@ -14859,8 +14919,8 @@
       <c r="J50" s="46" t="inlineStr">
         <is>
           <t>・role: NICHINO_ADMIN
-・Trong khoảng thời gian đối tượng có log trong phạm vi 5,000 dòng
-・Đã set điều kiện tìm kiếm phù hợp</t>
+・Trong khoảng thời gian đối tượng có log tồn tại
+・Đã set điều kiện tìm kiếm phù hợp (áp dụng cùng điều kiện tìm kiếm/thứ tự sắp xếp/page/per_page với danh sách)</t>
         </is>
       </c>
       <c r="K50" s="10" t="n"/>
@@ -14962,7 +15022,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Kết quả tìm kiếm được hiển thị, số dòng trong phạm vi 5,000 dòng
+            <t xml:space="preserve">Kết quả tìm kiếm được hiển thị
 </t>
           </r>
           <r>
@@ -14996,7 +15056,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Tiếng Nhật hiển thị đúng không bị lỗi font, toàn bộ record đều được bao gồm
+            <t xml:space="preserve">Tiếng Nhật hiển thị đúng không bị lỗi font, toàn bộ record của trang đang hiển thị đều được bao gồm (không phải xuất toàn bộ)
 </t>
           </r>
           <r>
@@ -15092,7 +15152,7 @@
       <c r="BP50" s="10" t="n"/>
       <c r="BQ50" s="11" t="n"/>
     </row>
-    <row r="51" ht="450" customHeight="1">
+    <row r="51" ht="48" customHeight="1">
       <c r="A51" s="44" t="n">
         <v>34</v>
       </c>
@@ -15105,209 +15165,35 @@
       <c r="D51" s="11" t="n"/>
       <c r="E51" s="46" t="inlineStr">
         <is>
-          <t>Lỗi xuất CSV khi vượt quá 5,000 dòng</t>
+          <t>【廃止】Lỗi xuất CSV khi vượt quá 5,000 dòng</t>
         </is>
       </c>
       <c r="F51" s="10" t="n"/>
       <c r="G51" s="10" t="n"/>
       <c r="H51" s="10" t="n"/>
       <c r="I51" s="11" t="n"/>
-      <c r="J51" s="46" t="inlineStr">
-        <is>
-          <t>・role: NICHINO_ADMIN
-・Trạng thái có hơn 5,001 dòng log khớp với điều kiện tìm kiếm</t>
-        </is>
-      </c>
+      <c r="J51" s="46" t="inlineStr"/>
       <c r="K51" s="10" t="n"/>
       <c r="L51" s="10" t="n"/>
       <c r="M51" s="10" t="n"/>
       <c r="N51" s="10" t="n"/>
       <c r="O51" s="10" t="n"/>
       <c r="P51" s="11" t="n"/>
-      <c r="Q51" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Chỉ định khoảng thời gian rộng (ví dụ: 365 ngày gần nhất), tìm kiếm với loại log「すべて」
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Xác nhận số kết quả tìm kiếm vượt quá 5,000 dòng
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Nhấn button「CSV出力」
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Kiểm tra response GET `/api/v1/log/export` trên tab Network của DevTools</t>
-          </r>
-        </is>
-      </c>
+      <c r="Q51" s="46" t="inlineStr"/>
       <c r="R51" s="10" t="n"/>
       <c r="S51" s="10" t="n"/>
       <c r="T51" s="10" t="n"/>
       <c r="U51" s="10" t="n"/>
       <c r="V51" s="10" t="n"/>
       <c r="W51" s="11" t="n"/>
-      <c r="X51" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Điều kiện tìm kiếm phạm vi rộng được set
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Số kết quả tìm kiếm hiển thị ở phía trên danh sách (vượt 5,000 dòng)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Hiển thị toast message lỗi `検索結果が5,000件を超えています。条件を絞り込んでください。`, CSV không được download
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Trả về HTTP 409 (`error_code: EXPORT_LIMIT_EXCEEDED`, message `検索結果が5,000件を超えています。条件を絞り込んでください。`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">補足：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Áp dụng verbatim văn bản của message code ACSMS-MSG-030-005
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Backend kiểm tra giới hạn bằng count query trước khi lấy data</t>
-          </r>
-        </is>
-      </c>
+      <c r="X51" s="46" t="inlineStr"/>
       <c r="Y51" s="10" t="n"/>
       <c r="Z51" s="10" t="n"/>
       <c r="AA51" s="10" t="n"/>
       <c r="AB51" s="10" t="n"/>
       <c r="AC51" s="10" t="n"/>
       <c r="AD51" s="11" t="n"/>
-      <c r="AE51" s="45" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="AE51" s="45" t="inlineStr"/>
       <c r="AF51" s="11" t="n"/>
       <c r="AG51" s="45" t="inlineStr"/>
       <c r="AH51" s="10" t="n"/>
